--- a/backtest_policy_configs/shock_overlay_policy.xlsx
+++ b/backtest_policy_configs/shock_overlay_policy.xlsx
@@ -504,7 +504,7 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>1</v>
+        <v>0.25</v>
       </c>
     </row>
     <row r="3">
@@ -519,7 +519,7 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>0.8</v>
+        <v>0.25</v>
       </c>
     </row>
     <row r="4">
@@ -534,7 +534,7 @@
         </is>
       </c>
       <c r="C4" t="n">
-        <v>0.6</v>
+        <v>0.25</v>
       </c>
     </row>
     <row r="5">
@@ -594,7 +594,7 @@
         </is>
       </c>
       <c r="C8" t="n">
-        <v>-0.7</v>
+        <v>-0.25</v>
       </c>
     </row>
     <row r="9">
@@ -609,7 +609,7 @@
         </is>
       </c>
       <c r="C9" t="n">
-        <v>-0.8</v>
+        <v>-0.25</v>
       </c>
     </row>
     <row r="10">
@@ -624,7 +624,7 @@
         </is>
       </c>
       <c r="C10" t="n">
-        <v>1</v>
+        <v>0.25</v>
       </c>
     </row>
     <row r="11">
@@ -639,7 +639,7 @@
         </is>
       </c>
       <c r="C11" t="n">
-        <v>0.5</v>
+        <v>0.25</v>
       </c>
     </row>
     <row r="12">
@@ -654,7 +654,7 @@
         </is>
       </c>
       <c r="C12" t="n">
-        <v>0.3</v>
+        <v>0.25</v>
       </c>
     </row>
     <row r="13">
@@ -714,7 +714,7 @@
         </is>
       </c>
       <c r="C16" t="n">
-        <v>-0.4</v>
+        <v>-0.25</v>
       </c>
     </row>
     <row r="17">
@@ -729,7 +729,7 @@
         </is>
       </c>
       <c r="C17" t="n">
-        <v>-0.5</v>
+        <v>-0.25</v>
       </c>
     </row>
     <row r="18">
@@ -819,7 +819,7 @@
         </is>
       </c>
       <c r="C23" t="n">
-        <v>-0.3</v>
+        <v>-0.25</v>
       </c>
     </row>
     <row r="24">
@@ -834,7 +834,7 @@
         </is>
       </c>
       <c r="C24" t="n">
-        <v>-0.5</v>
+        <v>-0.25</v>
       </c>
     </row>
     <row r="25">
@@ -849,7 +849,7 @@
         </is>
       </c>
       <c r="C25" t="n">
-        <v>-0.5</v>
+        <v>-0.25</v>
       </c>
     </row>
     <row r="26">
@@ -864,7 +864,7 @@
         </is>
       </c>
       <c r="C26" t="n">
-        <v>-1</v>
+        <v>-0.25</v>
       </c>
     </row>
     <row r="27">
@@ -879,7 +879,7 @@
         </is>
       </c>
       <c r="C27" t="n">
-        <v>0.7</v>
+        <v>0.25</v>
       </c>
     </row>
     <row r="28">
@@ -894,7 +894,7 @@
         </is>
       </c>
       <c r="C28" t="n">
-        <v>0.5</v>
+        <v>0.25</v>
       </c>
     </row>
     <row r="29">
@@ -909,7 +909,7 @@
         </is>
       </c>
       <c r="C29" t="n">
-        <v>0.4</v>
+        <v>0.25</v>
       </c>
     </row>
     <row r="30">
@@ -954,7 +954,7 @@
         </is>
       </c>
       <c r="C32" t="n">
-        <v>-0.3</v>
+        <v>-0.25</v>
       </c>
     </row>
     <row r="33">
@@ -969,7 +969,7 @@
         </is>
       </c>
       <c r="C33" t="n">
-        <v>-0.4</v>
+        <v>-0.25</v>
       </c>
     </row>
     <row r="34">
@@ -984,7 +984,7 @@
         </is>
       </c>
       <c r="C34" t="n">
-        <v>-0.8</v>
+        <v>-0.25</v>
       </c>
     </row>
     <row r="35">
@@ -999,7 +999,7 @@
         </is>
       </c>
       <c r="C35" t="n">
-        <v>-0.8</v>
+        <v>-0.25</v>
       </c>
     </row>
     <row r="36">
@@ -1014,7 +1014,7 @@
         </is>
       </c>
       <c r="C36" t="n">
-        <v>-1</v>
+        <v>-0.25</v>
       </c>
     </row>
     <row r="37">
@@ -1119,7 +1119,7 @@
         </is>
       </c>
       <c r="C43" t="n">
-        <v>-0.3</v>
+        <v>-0.25</v>
       </c>
     </row>
   </sheetData>
@@ -1241,10 +1241,10 @@
         <v>65</v>
       </c>
       <c r="H2" t="n">
-        <v>0.3</v>
+        <v>0.15</v>
       </c>
       <c r="I2" t="n">
-        <v>0.6</v>
+        <v>0.25</v>
       </c>
       <c r="J2" t="inlineStr">
         <is>
@@ -1277,7 +1277,7 @@
         <v>60</v>
       </c>
       <c r="H3" t="n">
-        <v>-0.6</v>
+        <v>-0.15</v>
       </c>
       <c r="J3" t="inlineStr">
         <is>
@@ -1310,7 +1310,7 @@
         <v>55</v>
       </c>
       <c r="H4" t="n">
-        <v>-0.8</v>
+        <v>-0.15</v>
       </c>
       <c r="J4" t="inlineStr">
         <is>
@@ -1343,10 +1343,10 @@
         <v>60</v>
       </c>
       <c r="H5" t="n">
-        <v>0.2</v>
+        <v>0.15</v>
       </c>
       <c r="I5" t="n">
-        <v>0.9</v>
+        <v>0.25</v>
       </c>
       <c r="J5" t="inlineStr">
         <is>
@@ -1379,7 +1379,7 @@
         <v>60</v>
       </c>
       <c r="H6" t="n">
-        <v>-0.2</v>
+        <v>-0.15</v>
       </c>
       <c r="J6" t="inlineStr">
         <is>

--- a/backtest_policy_configs/shock_overlay_policy.xlsx
+++ b/backtest_policy_configs/shock_overlay_policy.xlsx
@@ -460,7 +460,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C43"/>
+  <dimension ref="A1:C54"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="34" customWidth="1" min="1" max="1"/>
@@ -1120,6 +1120,171 @@
       </c>
       <c r="C43" t="n">
         <v>-0.25</v>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="inlineStr">
+        <is>
+          <t>METALS_MINING_SHOCK</t>
+        </is>
+      </c>
+      <c r="B44" t="inlineStr">
+        <is>
+          <t>Basic Materials</t>
+        </is>
+      </c>
+      <c r="C44" t="n">
+        <v>0.35</v>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="inlineStr">
+        <is>
+          <t>METALS_MINING_SHOCK</t>
+        </is>
+      </c>
+      <c r="B45" t="inlineStr">
+        <is>
+          <t>Energy</t>
+        </is>
+      </c>
+      <c r="C45" t="n">
+        <v>0.1</v>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="inlineStr">
+        <is>
+          <t>METALS_MINING_SHOCK</t>
+        </is>
+      </c>
+      <c r="B46" t="inlineStr">
+        <is>
+          <t>Industrials</t>
+        </is>
+      </c>
+      <c r="C46" t="n">
+        <v>0.05</v>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="inlineStr">
+        <is>
+          <t>METALS_MINING_SHOCK</t>
+        </is>
+      </c>
+      <c r="B47" t="inlineStr">
+        <is>
+          <t>Consumer Defensive</t>
+        </is>
+      </c>
+      <c r="C47" t="n">
+        <v>0.05</v>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="inlineStr">
+        <is>
+          <t>METALS_MINING_SHOCK</t>
+        </is>
+      </c>
+      <c r="B48" t="inlineStr">
+        <is>
+          <t>Communication Services</t>
+        </is>
+      </c>
+      <c r="C48" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="inlineStr">
+        <is>
+          <t>METALS_MINING_SHOCK</t>
+        </is>
+      </c>
+      <c r="B49" t="inlineStr">
+        <is>
+          <t>Consumer Cyclical</t>
+        </is>
+      </c>
+      <c r="C49" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="inlineStr">
+        <is>
+          <t>METALS_MINING_SHOCK</t>
+        </is>
+      </c>
+      <c r="B50" t="inlineStr">
+        <is>
+          <t>Healthcare</t>
+        </is>
+      </c>
+      <c r="C50" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="inlineStr">
+        <is>
+          <t>METALS_MINING_SHOCK</t>
+        </is>
+      </c>
+      <c r="B51" t="inlineStr">
+        <is>
+          <t>Financial Services</t>
+        </is>
+      </c>
+      <c r="C51" t="n">
+        <v>-0.1</v>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="inlineStr">
+        <is>
+          <t>METALS_MINING_SHOCK</t>
+        </is>
+      </c>
+      <c r="B52" t="inlineStr">
+        <is>
+          <t>Utilities</t>
+        </is>
+      </c>
+      <c r="C52" t="n">
+        <v>-0.1</v>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" t="inlineStr">
+        <is>
+          <t>METALS_MINING_SHOCK</t>
+        </is>
+      </c>
+      <c r="B53" t="inlineStr">
+        <is>
+          <t>Technology</t>
+        </is>
+      </c>
+      <c r="C53" t="n">
+        <v>-0.15</v>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" t="inlineStr">
+        <is>
+          <t>METALS_MINING_SHOCK</t>
+        </is>
+      </c>
+      <c r="B54" t="inlineStr">
+        <is>
+          <t>Real Estate</t>
+        </is>
+      </c>
+      <c r="C54" t="n">
+        <v>-0.2</v>
       </c>
     </row>
   </sheetData>
@@ -1143,7 +1308,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J8"/>
+  <dimension ref="A1:J11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="34" customWidth="1" min="1" max="1"/>
@@ -1459,6 +1624,117 @@
         </is>
       </c>
     </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>basic_materials_metals_mining_boost</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>METALS_MINING_SHOCK</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>Basic Materials</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>boost</t>
+        </is>
+      </c>
+      <c r="E9" t="n">
+        <v>60</v>
+      </c>
+      <c r="G9" t="n">
+        <v>70</v>
+      </c>
+      <c r="H9" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="I9" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="J9" t="inlineStr">
+        <is>
+          <t>LONG</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>technology_metals_mining_penalty</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>METALS_MINING_SHOCK</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>Technology</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>penalty</t>
+        </is>
+      </c>
+      <c r="E10" t="n">
+        <v>60</v>
+      </c>
+      <c r="H10" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="I10" t="n">
+        <v>-0.2</v>
+      </c>
+      <c r="J10" t="inlineStr">
+        <is>
+          <t>LONG</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>real_estate_metals_mining_penalty</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>METALS_MINING_SHOCK</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>Real Estate</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>penalty</t>
+        </is>
+      </c>
+      <c r="E11" t="n">
+        <v>60</v>
+      </c>
+      <c r="H11" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="I11" t="n">
+        <v>-0.25</v>
+      </c>
+      <c r="J11" t="inlineStr">
+        <is>
+          <t>LONG</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <autoFilter ref="A1:J8"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
